--- a/week03/Monthly_Report.xlsx
+++ b/week03/Monthly_Report.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="월별요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="카테고리별" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별카테고리요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="카테고리별합계" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,21 +414,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>총매출</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>평균매출</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>거래건수</t>
         </is>
@@ -436,101 +446,344 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>539500</v>
-      </c>
-      <c r="B2" t="n">
-        <v>7707.142857142857</v>
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>디저트</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>238000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8206.896551724138</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>226000</v>
-      </c>
-      <c r="B3" t="n">
-        <v>7533.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>베이커리</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>157500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7875</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>517000</v>
-      </c>
-      <c r="B4" t="n">
-        <v>7281.69014084507</v>
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>71</v>
+        <v>318500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8166.666666666667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>533000</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7724.63768115942</v>
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>디저트</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>69</v>
+        <v>257500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7573.529411764706</v>
+      </c>
+      <c r="E5" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>339500</v>
-      </c>
-      <c r="B6" t="n">
-        <v>9700</v>
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>베이커리</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>78500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9812.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>460000</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7076.923076923077</v>
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>65</v>
+        <v>314000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7850</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>528000</v>
-      </c>
-      <c r="B8" t="n">
-        <v>7333.333333333333</v>
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>디저트</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>176500</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6537.037037037037</v>
+      </c>
+      <c r="E8" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>272500</v>
-      </c>
-      <c r="B9" t="n">
-        <v>8790.322580645161</v>
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>베이커리</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>151500</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10821.42857142857</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>420500</v>
-      </c>
-      <c r="B10" t="n">
-        <v>6893.44262295082</v>
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>312500</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7621.951219512195</v>
+      </c>
+      <c r="E10" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>디저트</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>208000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7428.571428571428</v>
+      </c>
+      <c r="E11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>베이커리</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9857.142857142857</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>323000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7511.627906976744</v>
+      </c>
+      <c r="E13" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>디저트</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>201000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7730.76923076923</v>
+      </c>
+      <c r="E14" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>베이커리</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>145500</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8558.823529411764</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>354000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7375</v>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>디저트</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>259000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8354.838709677419</v>
+      </c>
+      <c r="E17" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>베이커리</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10062.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>293000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7325</v>
+      </c>
+      <c r="E19" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -550,43 +803,43 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>카테고리</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>총매출</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>디저트</t>
+          <t>음료</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1600500</v>
+        <v>1915000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>베이커리</t>
+          <t>디저트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>838000</v>
+        <v>1340000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>음료</t>
+          <t>베이커리</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1397500</v>
+        <v>682500</v>
       </c>
     </row>
   </sheetData>
